--- a/public/templates/examples/A-083-RiskFindingRegister-EXAMPLE-L.xlsx
+++ b/public/templates/examples/A-083-RiskFindingRegister-EXAMPLE-L.xlsx
@@ -19,7 +19,7 @@
   <numFmts count="0"/>
   <fonts count="8">
     <font>
-      <name val="Calibri"/>
+      <name val="Aptos"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
@@ -224,12 +224,12 @@
 <wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
-      <col>0</col>
+      <col>9</col>
       <colOff>0</colOff>
       <row>0</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="552450" cy="552450"/>
+    <ext cx="857250" cy="857250"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
@@ -343,7 +343,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Aptos"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -377,7 +377,7 @@
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Aptos"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>

--- a/public/templates/examples/A-083-RiskFindingRegister-EXAMPLE-L.xlsx
+++ b/public/templates/examples/A-083-RiskFindingRegister-EXAMPLE-L.xlsx
@@ -4,19 +4,21 @@
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Form" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
+  </numFmts>
   <fonts count="8">
     <font>
       <name val="Aptos"/>
@@ -111,7 +113,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -144,6 +146,10 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf applyNumberFormat="1" numFmtId="164" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf applyNumberFormat="1" numFmtId="164" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -587,7 +593,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:J39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -739,7 +745,7 @@
         </is>
       </c>
     </row>
-    <row r="13" ht="32" customHeight="1">
+    <row r="13" ht="34.7" customHeight="1">
       <c r="A13" s="8" t="inlineStr">
         <is>
           <t>Finding ID</t>
@@ -791,7 +797,7 @@
         </is>
       </c>
     </row>
-    <row r="14">
+    <row r="14" ht="34.7" customHeight="1">
       <c r="A14" s="9" t="inlineStr">
         <is>
           <t>F-01</t>
@@ -827,10 +833,8 @@
           <t>Reinstall and monitor agent coverage in the SIEM</t>
         </is>
       </c>
-      <c r="H14" s="9" t="inlineStr">
-        <is>
-          <t>2026-05-20</t>
-        </is>
+      <c r="H14" s="14">
+        <v>46162</v>
       </c>
       <c r="I14" s="9" t="inlineStr">
         <is>
@@ -843,7 +847,7 @@
         </is>
       </c>
     </row>
-    <row r="15">
+    <row r="15" ht="34.7" customHeight="1">
       <c r="A15" s="9" t="inlineStr">
         <is>
           <t>F-02</t>
@@ -879,10 +883,8 @@
           <t>Patch and revalidate the GIS feed</t>
         </is>
       </c>
-      <c r="H15" s="9" t="inlineStr">
-        <is>
-          <t>2026-05-31</t>
-        </is>
+      <c r="H15" s="14">
+        <v>46173</v>
       </c>
       <c r="I15" s="9" t="inlineStr">
         <is>
@@ -895,7 +897,7 @@
         </is>
       </c>
     </row>
-    <row r="16">
+    <row r="16" ht="50.5" customHeight="1">
       <c r="A16" s="9" t="inlineStr">
         <is>
           <t>F-03</t>
@@ -931,10 +933,8 @@
           <t>Stand up quarterly privileged-access recertification</t>
         </is>
       </c>
-      <c r="H16" s="9" t="inlineStr">
-        <is>
-          <t>2026-07-15</t>
-        </is>
+      <c r="H16" s="14">
+        <v>46218</v>
       </c>
       <c r="I16" s="9" t="inlineStr">
         <is>
@@ -943,7 +943,7 @@
       </c>
       <c r="J16" s="9" t="inlineStr"/>
     </row>
-    <row r="17">
+    <row r="17" ht="34.7" customHeight="1">
       <c r="A17" s="9" t="inlineStr">
         <is>
           <t>F-04</t>
@@ -979,10 +979,8 @@
           <t>Disable TLS 1.0/1.1 on the service</t>
         </is>
       </c>
-      <c r="H17" s="9" t="inlineStr">
-        <is>
-          <t>2026-06-30</t>
-        </is>
+      <c r="H17" s="14">
+        <v>46203</v>
       </c>
       <c r="I17" s="9" t="inlineStr">
         <is>
@@ -991,7 +989,7 @@
       </c>
       <c r="J17" s="9" t="inlineStr"/>
     </row>
-    <row r="18">
+    <row r="18" ht="34.7" customHeight="1">
       <c r="A18" s="9" t="inlineStr">
         <is>
           <t>F-05</t>
@@ -1027,10 +1025,8 @@
           <t>Revise and re-exercise the continuity runbook</t>
         </is>
       </c>
-      <c r="H18" s="9" t="inlineStr">
-        <is>
-          <t>2026-06-15</t>
-        </is>
+      <c r="H18" s="14">
+        <v>46188</v>
       </c>
       <c r="I18" s="9" t="inlineStr">
         <is>
@@ -1039,7 +1035,7 @@
       </c>
       <c r="J18" s="9" t="inlineStr"/>
     </row>
-    <row r="19">
+    <row r="19" ht="34.7" customHeight="1">
       <c r="A19" s="9" t="inlineStr">
         <is>
           <t>F-06</t>
@@ -1075,10 +1071,8 @@
           <t>Tune SIEM rule and on-call escalation</t>
         </is>
       </c>
-      <c r="H19" s="9" t="inlineStr">
-        <is>
-          <t>2026-05-25</t>
-        </is>
+      <c r="H19" s="14">
+        <v>46167</v>
       </c>
       <c r="I19" s="9" t="inlineStr">
         <is>
@@ -1091,7 +1085,7 @@
         </is>
       </c>
     </row>
-    <row r="20">
+    <row r="20" ht="34.7" customHeight="1">
       <c r="A20" s="9" t="inlineStr">
         <is>
           <t>F-07</t>
@@ -1127,10 +1121,8 @@
           <t>Accepted for this cycle; tracked in the decisions log</t>
         </is>
       </c>
-      <c r="H20" s="9" t="inlineStr">
-        <is>
-          <t>2026-07-01</t>
-        </is>
+      <c r="H20" s="14">
+        <v>46204</v>
       </c>
       <c r="I20" s="9" t="inlineStr">
         <is>
@@ -1146,7 +1138,7 @@
     <row r="22">
       <c r="A22" s="6" t="inlineStr">
         <is>
-          <t>Status Summary</t>
+          <t>Status Summary (as of 2026-06-16)</t>
         </is>
       </c>
     </row>
@@ -1158,7 +1150,6 @@
       </c>
       <c r="C23" s="11">
         <f>COUNTA(A14:A20)</f>
-        <v/>
       </c>
     </row>
     <row r="24">
@@ -1169,7 +1160,6 @@
       </c>
       <c r="C24" s="11">
         <f>COUNTIF(I14:I20,"Open")</f>
-        <v/>
       </c>
     </row>
     <row r="25">
@@ -1180,7 +1170,6 @@
       </c>
       <c r="C25" s="11">
         <f>COUNTIF(I14:I20,"In Progress")</f>
-        <v/>
       </c>
     </row>
     <row r="26">
@@ -1190,8 +1179,7 @@
         </is>
       </c>
       <c r="C26" s="11">
-        <f>COUNTIFS(H14:H20,"&lt;"&amp;TODAY(),I14:I20,"Open")+COUNTIFS(H14:H20,"&lt;"&amp;TODAY(),I14:I20,"In Progress")</f>
-        <v/>
+        <f>COUNTIFS(H14:H20,"&lt;"&amp;DATE(2026,6,16),I14:I20,"Open")+COUNTIFS(H14:H20,"&lt;"&amp;DATE(2026,6,16),I14:I20,"In Progress")</f>
       </c>
     </row>
     <row r="27">
@@ -1202,7 +1190,6 @@
       </c>
       <c r="C27" s="11">
         <f>COUNTIF(I14:I20,"Risk Accepted")</f>
-        <v/>
       </c>
     </row>
     <row r="28">
@@ -1213,7 +1200,6 @@
       </c>
       <c r="C28" s="11">
         <f>COUNTIF(I14:I20,"Closed")</f>
-        <v/>
       </c>
     </row>
     <row r="29">
@@ -1282,10 +1268,8 @@
           <t>(on file)</t>
         </is>
       </c>
-      <c r="D34" s="13" t="inlineStr">
-        <is>
-          <t>2026-06-01</t>
-        </is>
+      <c r="D34" s="15">
+        <v>46174</v>
       </c>
     </row>
     <row r="35" ht="22" customHeight="1">
@@ -1304,10 +1288,8 @@
           <t>Dr. Lisa Park</t>
         </is>
       </c>
-      <c r="D35" s="13" t="inlineStr">
-        <is>
-          <t>2026-06-01</t>
-        </is>
+      <c r="D35" s="15">
+        <v>46174</v>
       </c>
     </row>
     <row r="37">
@@ -1339,16 +1321,14 @@
         </is>
       </c>
     </row>
-    <row r="39">
+    <row r="39" ht="34.7" customHeight="1">
       <c r="A39" s="9" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="B39" s="9" t="inlineStr">
-        <is>
-          <t>2026-06-01</t>
-        </is>
+      <c r="B39" s="14">
+        <v>46174</v>
       </c>
       <c r="C39" s="9" t="inlineStr">
         <is>
@@ -1391,7 +1371,8 @@
     <mergeCell ref="A12:J12"/>
     <mergeCell ref="A2:J2"/>
   </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="1" orientation="landscape" fitToWidth="1" fitToHeight="0"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>